--- a/Open Data Dashboard/Databricks/ae outputs/hospital_model_performance_yes.xlsx
+++ b/Open Data Dashboard/Databricks/ae outputs/hospital_model_performance_yes.xlsx
@@ -408,10 +408,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>47.42216182583942</v>
+        <v>44.81705727879428</v>
       </c>
       <c r="C2">
-        <v>0.6693254720884173</v>
+        <v>0.7048998886717373</v>
       </c>
       <c r="D2">
         <v>1211.402777777778</v>
@@ -420,7 +420,7 @@
         <v>500</v>
       </c>
       <c r="F2">
-        <v>0.03914648595476363</v>
+        <v>0.03699600009256014</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>33.53027572826489</v>
+        <v>33.05907261717342</v>
       </c>
       <c r="C3">
-        <v>0.6624219691862944</v>
+        <v>0.67137629052119</v>
       </c>
       <c r="D3">
         <v>644.4583333333334</v>
@@ -457,7 +457,7 @@
         <v>500</v>
       </c>
       <c r="F3">
-        <v>0.05202861689263318</v>
+        <v>0.05129745540907494</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>29.49449925574017</v>
+        <v>28.55132505462418</v>
       </c>
       <c r="C4">
-        <v>0.5629513455634025</v>
+        <v>0.5880289349904768</v>
       </c>
       <c r="D4">
         <v>629.8243243243244</v>
@@ -494,7 +494,7 @@
         <v>500</v>
       </c>
       <c r="F4">
-        <v>0.0468297239668885</v>
+        <v>0.04533220447662775</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>16.02931526158152</v>
+        <v>14.73067385262597</v>
       </c>
       <c r="C5">
-        <v>0.5130742680381797</v>
+        <v>0.5854049077208063</v>
       </c>
       <c r="D5">
         <v>176.1081081081081</v>
@@ -531,7 +531,7 @@
         <v>500</v>
       </c>
       <c r="F5">
-        <v>0.09101974596048437</v>
+        <v>0.08364563114597312</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>30.82312135951253</v>
+        <v>28.59973474154552</v>
       </c>
       <c r="C6">
-        <v>0.3031845079792398</v>
+        <v>0.3784159950015327</v>
       </c>
       <c r="D6">
         <v>560.4324324324324</v>
@@ -568,7 +568,7 @@
         <v>500</v>
       </c>
       <c r="F6">
-        <v>0.05499881801224749</v>
+        <v>0.0510315482946173</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>37.11427789121399</v>
+        <v>35.8612545515846</v>
       </c>
       <c r="C7">
-        <v>0.6239803774422255</v>
+        <v>0.6477075454785278</v>
       </c>
       <c r="D7">
         <v>1077.837837837838</v>
@@ -605,7 +605,7 @@
         <v>500</v>
       </c>
       <c r="F7">
-        <v>0.03443400907660275</v>
+        <v>0.03327147488487037</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>41.41007467502563</v>
+        <v>39.94585889356822</v>
       </c>
       <c r="C8">
-        <v>0.729234791817825</v>
+        <v>0.7478624886109133</v>
       </c>
       <c r="D8">
         <v>1331.351351351351</v>
@@ -642,7 +642,7 @@
         <v>500</v>
       </c>
       <c r="F8">
-        <v>0.03110379137182194</v>
+        <v>0.03000399470284256</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>63.79817450069788</v>
+        <v>61.55065370784428</v>
       </c>
       <c r="C9">
-        <v>0.5164098829685845</v>
+        <v>0.5460642164950222</v>
       </c>
       <c r="D9">
         <v>1606.959459459459</v>
@@ -679,7 +679,7 @@
         <v>500</v>
       </c>
       <c r="F9">
-        <v>0.03970117237566029</v>
+        <v>0.03830255539150215</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>64.10004084305048</v>
+        <v>61.44307200859443</v>
       </c>
       <c r="C10">
-        <v>0.5401058310430932</v>
+        <v>0.5681051516974719</v>
       </c>
       <c r="D10">
         <v>1936.189189189189</v>
@@ -716,7 +716,7 @@
         <v>500</v>
       </c>
       <c r="F10">
-        <v>0.03310629002628272</v>
+        <v>0.03173402286907961</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>101.7189801300488</v>
+        <v>96.47226461734583</v>
       </c>
       <c r="C11">
-        <v>0.6561526513506196</v>
+        <v>0.6903116955774782</v>
       </c>
       <c r="D11">
         <v>1444.905405405405</v>
@@ -753,7 +753,7 @@
         <v>500</v>
       </c>
       <c r="F11">
-        <v>0.07039836639098801</v>
+        <v>0.06676718368997869</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>15.06574412621994</v>
+        <v>14.46025430573647</v>
       </c>
       <c r="C12">
-        <v>0.4852770463305528</v>
+        <v>0.5203338449092897</v>
       </c>
       <c r="D12">
         <v>185.3108108108108</v>
@@ -790,7 +790,7 @@
         <v>500</v>
       </c>
       <c r="F12">
-        <v>0.08129986621018562</v>
+        <v>0.07803243773240713</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>30.60038880326119</v>
+        <v>29.37113737104123</v>
       </c>
       <c r="C13">
-        <v>0.7373467799711809</v>
+        <v>0.758074007511885</v>
       </c>
       <c r="D13">
         <v>763.9324324324324</v>
@@ -827,7 +827,7 @@
         <v>500</v>
       </c>
       <c r="F13">
-        <v>0.04005640748335123</v>
+        <v>0.03844729733167732</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>16.35859292148228</v>
+        <v>15.46723081544823</v>
       </c>
       <c r="C14">
-        <v>0.7746794119122832</v>
+        <v>0.7952499253199332</v>
       </c>
       <c r="D14">
         <v>179.5405405405405</v>
@@ -864,7 +864,7 @@
         <v>500</v>
       </c>
       <c r="F14">
-        <v>0.09111364415096257</v>
+        <v>0.08614895983314534</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>41.40113928331269</v>
+        <v>40.59821723786782</v>
       </c>
       <c r="C15">
-        <v>0.6565005719844849</v>
+        <v>0.671131384476028</v>
       </c>
       <c r="D15">
         <v>1240.108108108108</v>
@@ -901,7 +901,7 @@
         <v>500</v>
       </c>
       <c r="F15">
-        <v>0.03338510490546966</v>
+        <v>0.03273764357512661</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>45.26419301624794</v>
+        <v>45.07467875937916</v>
       </c>
       <c r="C16">
-        <v>0.6558730066886996</v>
+        <v>0.6616126327488164</v>
       </c>
       <c r="D16">
         <v>1222.675675675676</v>
@@ -938,7 +938,7 @@
         <v>500</v>
       </c>
       <c r="F16">
-        <v>0.03702060482329791</v>
+        <v>0.03686560521004065</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>45.15517063445307</v>
+        <v>44.66516068329877</v>
       </c>
       <c r="C17">
-        <v>0.6384444231327725</v>
+        <v>0.6463380031135497</v>
       </c>
       <c r="D17">
         <v>1347</v>
@@ -975,7 +975,7 @@
         <v>500</v>
       </c>
       <c r="F17">
-        <v>0.03352276958756724</v>
+        <v>0.03315899085619805</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>34.22089533674215</v>
+        <v>32.94325883413913</v>
       </c>
       <c r="C18">
-        <v>0.7635320751155631</v>
+        <v>0.7811537868798101</v>
       </c>
       <c r="D18">
         <v>1091.013513513514</v>
@@ -1012,7 +1012,7 @@
         <v>500</v>
       </c>
       <c r="F18">
-        <v>0.0313661516680364</v>
+        <v>0.03019509696818351</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>34.00005108174519</v>
+        <v>32.75861675748062</v>
       </c>
       <c r="C19">
-        <v>0.6369474336108571</v>
+        <v>0.6609110255278573</v>
       </c>
       <c r="D19">
         <v>351.1486486486486</v>
@@ -1049,7 +1049,7 @@
         <v>500</v>
       </c>
       <c r="F19">
-        <v>0.09682523686931477</v>
+        <v>0.09328988416600216</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>29.11524316306741</v>
+        <v>28.53684106819441</v>
       </c>
       <c r="C20">
-        <v>0.6558134846864779</v>
+        <v>0.6674169627095471</v>
       </c>
       <c r="D20">
         <v>506.5405405405405</v>
@@ -1086,7 +1086,7 @@
         <v>500</v>
       </c>
       <c r="F20">
-        <v>0.0574786040461794</v>
+        <v>0.05633673671556894</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>14.45531266133727</v>
+        <v>14.31966862399</v>
       </c>
       <c r="C21">
-        <v>0.5037202865985388</v>
+        <v>0.5176833858337517</v>
       </c>
       <c r="D21">
         <v>147.2027027027027</v>
@@ -1123,7 +1123,7 @@
         <v>500</v>
       </c>
       <c r="F21">
-        <v>0.09820004929211031</v>
+        <v>0.09727857139220231</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>37.00030402007116</v>
+        <v>35.41084732186489</v>
       </c>
       <c r="C22">
-        <v>0.7235372808549626</v>
+        <v>0.7461332638156679</v>
       </c>
       <c r="D22">
         <v>1100.662162162162</v>
@@ -1160,7 +1160,7 @@
         <v>500</v>
       </c>
       <c r="F22">
-        <v>0.03361640409931695</v>
+        <v>0.03217231275789761</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>75.15767017990805</v>
+        <v>73.85715158652863</v>
       </c>
       <c r="C23">
-        <v>0.6470033440114255</v>
+        <v>0.6612365378391437</v>
       </c>
       <c r="D23">
         <v>2402.175675675676</v>
@@ -1197,7 +1197,7 @@
         <v>500</v>
       </c>
       <c r="F23">
-        <v>0.0312873329544343</v>
+        <v>0.03074594099607405</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>76.4519166460486</v>
+        <v>75.84421773075616</v>
       </c>
       <c r="C24">
-        <v>0.6872476683022619</v>
+        <v>0.6920940091069966</v>
       </c>
       <c r="D24">
         <v>1028.351351351351</v>
@@ -1234,7 +1234,7 @@
         <v>500</v>
       </c>
       <c r="F24">
-        <v>0.07434415926578355</v>
+        <v>0.07375321443501742</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>42.01812563513354</v>
+        <v>40.39950244213524</v>
       </c>
       <c r="C25">
-        <v>0.675051211328933</v>
+        <v>0.6982971089196301</v>
       </c>
       <c r="D25">
         <v>1186.959459459459</v>
@@ -1271,7 +1271,7 @@
         <v>500</v>
       </c>
       <c r="F25">
-        <v>0.03539979845164094</v>
+        <v>0.03403612660918777</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>26.97032104406779</v>
+        <v>26.14707562923531</v>
       </c>
       <c r="C26">
-        <v>0.5857400153394303</v>
+        <v>0.6100253932865453</v>
       </c>
       <c r="D26">
         <v>450.027027027027</v>
@@ -1308,7 +1308,7 @@
         <v>500</v>
       </c>
       <c r="F26">
-        <v>0.05993044733832852</v>
+        <v>0.05810112295247771</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>37.64260220950053</v>
+        <v>35.88443471364169</v>
       </c>
       <c r="C27">
-        <v>0.6947970885040009</v>
+        <v>0.7220886434281553</v>
       </c>
       <c r="D27">
         <v>1172.797297297297</v>
@@ -1345,7 +1345,7 @@
         <v>500</v>
       </c>
       <c r="F27">
-        <v>0.03209642646367589</v>
+        <v>0.03059730338425668</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>11.28728458765036</v>
+        <v>11.45898945891048</v>
       </c>
       <c r="C28">
-        <v>0.5115137137171388</v>
+        <v>0.5058819976701171</v>
       </c>
       <c r="D28">
         <v>111.3108108108108</v>
@@ -1382,7 +1382,7 @@
         <v>500</v>
       </c>
       <c r="F28">
-        <v>0.1014033093949407</v>
+        <v>0.1029458807769061</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>18.4611380360068</v>
+        <v>18.44840142933608</v>
       </c>
       <c r="C29">
-        <v>0.4443828159463627</v>
+        <v>0.4460759773766749</v>
       </c>
       <c r="D29">
         <v>264.6216216216216</v>
@@ -1419,7 +1419,7 @@
         <v>500</v>
       </c>
       <c r="F29">
-        <v>0.06976428427456353</v>
+        <v>0.06971615288381525</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>32.77042229113566</v>
+        <v>32.48977879442344</v>
       </c>
       <c r="C30">
-        <v>0.7793222550711674</v>
+        <v>0.7829583335185124</v>
       </c>
       <c r="D30">
         <v>698.0405405405405</v>
@@ -1456,7 +1456,7 @@
         <v>500</v>
       </c>
       <c r="F30">
-        <v>0.04694630238203541</v>
+        <v>0.04654425768632919</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>13.80523663426578</v>
+        <v>13.6256210546698</v>
       </c>
       <c r="C31">
-        <v>0.4530578913099834</v>
+        <v>0.4715510520880196</v>
       </c>
       <c r="D31">
         <v>161.3108108108108</v>
@@ -1493,7 +1493,7 @@
         <v>500</v>
       </c>
       <c r="F31">
-        <v>0.08558159595674522</v>
+        <v>0.08446812080468838</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>39.20947030153372</v>
+        <v>41.1253959650297</v>
       </c>
       <c r="C32">
-        <v>0.7771440429264839</v>
+        <v>0.7547636114756577</v>
       </c>
       <c r="D32">
         <v>1211.402777777778</v>
@@ -1530,7 +1530,7 @@
         <v>1000</v>
       </c>
       <c r="F32">
-        <v>0.03236699718772346</v>
+        <v>0.03394857327343345</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>33.62822033447108</v>
+        <v>34.57353902991185</v>
       </c>
       <c r="C33">
-        <v>0.6603689847650306</v>
+        <v>0.6424588135871219</v>
       </c>
       <c r="D33">
         <v>644.4583333333334</v>
@@ -1567,7 +1567,7 @@
         <v>1000</v>
       </c>
       <c r="F33">
-        <v>0.05218059662683817</v>
+        <v>0.0536474388516121</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>28.73367003269197</v>
+        <v>28.8873388660721</v>
       </c>
       <c r="C34">
-        <v>0.5824497457836637</v>
+        <v>0.5778532726089152</v>
       </c>
       <c r="D34">
         <v>629.8243243243244</v>
@@ -1604,7 +1604,7 @@
         <v>1000</v>
       </c>
       <c r="F34">
-        <v>0.04562172168170459</v>
+        <v>0.04586570850064014</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>16.08973879772298</v>
+        <v>16.22296703164079</v>
       </c>
       <c r="C35">
-        <v>0.5050454353129628</v>
+        <v>0.4972704173525279</v>
       </c>
       <c r="D35">
         <v>176.1081081081081</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="F35">
-        <v>0.09136285075441226</v>
+        <v>0.09211936466708247</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>30.24181190424629</v>
+        <v>30.02945218125796</v>
       </c>
       <c r="C36">
-        <v>0.3226557450269126</v>
+        <v>0.3296731046365465</v>
       </c>
       <c r="D36">
         <v>560.4324324324324</v>
@@ -1678,7 +1678,7 @@
         <v>1000</v>
       </c>
       <c r="F36">
-        <v>0.0539615663800691</v>
+        <v>0.05358264519225234</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>34.30827262059579</v>
+        <v>34.61392631118017</v>
       </c>
       <c r="C37">
-        <v>0.6776223201442536</v>
+        <v>0.673199423125903</v>
       </c>
       <c r="D37">
         <v>1077.837837837838</v>
@@ -1715,7 +1715,7 @@
         <v>1000</v>
       </c>
       <c r="F37">
-        <v>0.03183064410637021</v>
+        <v>0.03211422451137579</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>35.20696691061993</v>
+        <v>34.9434910169571</v>
       </c>
       <c r="C38">
-        <v>0.8050743330365221</v>
+        <v>0.8076129210327218</v>
       </c>
       <c r="D38">
         <v>1331.351351351351</v>
@@ -1752,7 +1752,7 @@
         <v>1000</v>
       </c>
       <c r="F38">
-        <v>0.02644453462632841</v>
+        <v>0.02624663352877412</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>62.35748089321159</v>
+        <v>62.43301533087152</v>
       </c>
       <c r="C39">
-        <v>0.5358134638080242</v>
+        <v>0.5365616488926956</v>
       </c>
       <c r="D39">
         <v>1606.959459459459</v>
@@ -1789,7 +1789,7 @@
         <v>1000</v>
       </c>
       <c r="F39">
-        <v>0.03880463849049875</v>
+        <v>0.03885164306003863</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>61.41505525043712</v>
+        <v>61.03438943781005</v>
       </c>
       <c r="C40">
-        <v>0.5728624615821764</v>
+        <v>0.5785092002660625</v>
       </c>
       <c r="D40">
         <v>1936.189189189189</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="F40">
-        <v>0.03171955281712717</v>
+        <v>0.03152294712655079</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>85.95147140418952</v>
+        <v>86.63973985965264</v>
       </c>
       <c r="C41">
-        <v>0.7539258210708917</v>
+        <v>0.7500293278621409</v>
       </c>
       <c r="D41">
         <v>1444.905405405405</v>
@@ -1863,7 +1863,7 @@
         <v>1000</v>
       </c>
       <c r="F41">
-        <v>0.05948588127820978</v>
+        <v>0.05996222281094147</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>15.58954953556055</v>
+        <v>15.91131269296743</v>
       </c>
       <c r="C42">
-        <v>0.4551110236435941</v>
+        <v>0.4347662091017626</v>
       </c>
       <c r="D42">
         <v>185.3108108108108</v>
@@ -1900,7 +1900,7 @@
         <v>1000</v>
       </c>
       <c r="F42">
-        <v>0.08412649789480645</v>
+        <v>0.0858628410471516</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>30.23845695478743</v>
+        <v>30.1953349999208</v>
       </c>
       <c r="C43">
-        <v>0.7460937175771891</v>
+        <v>0.7455040383504619</v>
       </c>
       <c r="D43">
         <v>763.9324324324324</v>
@@ -1937,7 +1937,7 @@
         <v>1000</v>
       </c>
       <c r="F43">
-        <v>0.03958263279712494</v>
+        <v>0.03952618545566396</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>16.19415178156256</v>
+        <v>16.40044935166527</v>
       </c>
       <c r="C44">
-        <v>0.7732986035581633</v>
+        <v>0.7680699953514544</v>
       </c>
       <c r="D44">
         <v>179.5405405405405</v>
@@ -1974,7 +1974,7 @@
         <v>1000</v>
       </c>
       <c r="F44">
-        <v>0.09019774438022198</v>
+        <v>0.09134677495282477</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>35.80181191913497</v>
+        <v>36.50998219637515</v>
       </c>
       <c r="C45">
-        <v>0.7411445474426663</v>
+        <v>0.7314834710785216</v>
       </c>
       <c r="D45">
         <v>1240.108108108108</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="F45">
-        <v>0.02886991197384696</v>
+        <v>0.02944096724927819</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>39.91762776454329</v>
+        <v>39.9757352686627</v>
       </c>
       <c r="C46">
-        <v>0.7310698570506916</v>
+        <v>0.7307253253551107</v>
       </c>
       <c r="D46">
         <v>1222.675675675676</v>
@@ -2048,7 +2048,7 @@
         <v>1000</v>
       </c>
       <c r="F46">
-        <v>0.03264776470054824</v>
+        <v>0.0326952895718411</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>40.16010082189563</v>
+        <v>39.69428382428703</v>
       </c>
       <c r="C47">
-        <v>0.7151356269944567</v>
+        <v>0.7259554569270492</v>
       </c>
       <c r="D47">
         <v>1347</v>
@@ -2085,7 +2085,7 @@
         <v>1000</v>
       </c>
       <c r="F47">
-        <v>0.02981447722486684</v>
+        <v>0.02946865911231405</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>31.16255382660802</v>
+        <v>31.06168099878531</v>
       </c>
       <c r="C48">
-        <v>0.8050314524749138</v>
+        <v>0.8064802763782867</v>
       </c>
       <c r="D48">
         <v>1091.013513513514</v>
@@ -2122,7 +2122,7 @@
         <v>1000</v>
       </c>
       <c r="F48">
-        <v>0.02856294027582825</v>
+        <v>0.02847048236712842</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>33.74157045625262</v>
+        <v>33.97586476936002</v>
       </c>
       <c r="C49">
-        <v>0.6413208235730021</v>
+        <v>0.6364211551783211</v>
       </c>
       <c r="D49">
         <v>351.1486486486486</v>
@@ -2159,7 +2159,7 @@
         <v>1000</v>
       </c>
       <c r="F49">
-        <v>0.09608913656966304</v>
+        <v>0.096756359166159</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>29.33342062245616</v>
+        <v>29.28836904522342</v>
       </c>
       <c r="C50">
-        <v>0.6487036438223823</v>
+        <v>0.6513916680017532</v>
       </c>
       <c r="D50">
         <v>506.5405405405405</v>
@@ -2196,7 +2196,7 @@
         <v>1000</v>
       </c>
       <c r="F50">
-        <v>0.05790932467350753</v>
+        <v>0.05782038494681818</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>14.35043967153026</v>
+        <v>14.34549560344652</v>
       </c>
       <c r="C51">
-        <v>0.5111144840315026</v>
+        <v>0.5096006032694144</v>
       </c>
       <c r="D51">
         <v>147.2027027027027</v>
@@ -2233,7 +2233,7 @@
         <v>1000</v>
       </c>
       <c r="F51">
-        <v>0.09748760999662524</v>
+        <v>0.09745402319425708</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>33.40318910573838</v>
+        <v>33.63375335902244</v>
       </c>
       <c r="C52">
-        <v>0.7749525716688767</v>
+        <v>0.7718749075349061</v>
       </c>
       <c r="D52">
         <v>1100.662162162162</v>
@@ -2270,7 +2270,7 @@
         <v>1000</v>
       </c>
       <c r="F52">
-        <v>0.03034826693789537</v>
+        <v>0.03055774470610641</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>78.93548641594549</v>
+        <v>77.14447190001842</v>
       </c>
       <c r="C53">
-        <v>0.6190226404145251</v>
+        <v>0.6304466597738925</v>
       </c>
       <c r="D53">
         <v>2402.175675675676</v>
@@ -2307,7 +2307,7 @@
         <v>1000</v>
       </c>
       <c r="F53">
-        <v>0.03285999738289032</v>
+        <v>0.03211441722650842</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>66.01454398446735</v>
+        <v>67.76025964470385</v>
       </c>
       <c r="C54">
-        <v>0.7671495523155248</v>
+        <v>0.7548705552131058</v>
       </c>
       <c r="D54">
         <v>1028.351351351351</v>
@@ -2344,7 +2344,7 @@
         <v>1000</v>
       </c>
       <c r="F54">
-        <v>0.06419454197023029</v>
+        <v>0.06589212875119038</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>35.39896279622451</v>
+        <v>36.25069832988252</v>
       </c>
       <c r="C55">
-        <v>0.7695720510429949</v>
+        <v>0.7571621680613008</v>
       </c>
       <c r="D55">
         <v>1186.959459459459</v>
@@ -2381,7 +2381,7 @@
         <v>1000</v>
       </c>
       <c r="F55">
-        <v>0.02982322817692963</v>
+        <v>0.03054080578825419</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>26.55224955012626</v>
+        <v>26.92781103276152</v>
       </c>
       <c r="C56">
-        <v>0.5914253337865446</v>
+        <v>0.5842493545828912</v>
       </c>
       <c r="D56">
         <v>450.027027027027</v>
@@ -2418,7 +2418,7 @@
         <v>1000</v>
       </c>
       <c r="F56">
-        <v>0.05900145536932747</v>
+        <v>0.05983598631987126</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>32.45888384501842</v>
+        <v>33.21174832831714</v>
       </c>
       <c r="C57">
-        <v>0.7720511572947024</v>
+        <v>0.7613455160139662</v>
       </c>
       <c r="D57">
         <v>1172.797297297297</v>
@@ -2455,7 +2455,7 @@
         <v>1000</v>
       </c>
       <c r="F57">
-        <v>0.02767646542144979</v>
+        <v>0.02831840455708191</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>11.20753241420388</v>
+        <v>10.98386879036859</v>
       </c>
       <c r="C58">
-        <v>0.4949952140979509</v>
+        <v>0.5160059355097142</v>
       </c>
       <c r="D58">
         <v>111.3108108108108</v>
@@ -2492,7 +2492,7 @@
         <v>1000</v>
       </c>
       <c r="F58">
-        <v>0.1006868275647793</v>
+        <v>0.09867746636970685</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>18.45905660578705</v>
+        <v>18.24710416463728</v>
       </c>
       <c r="C59">
-        <v>0.4463963754815301</v>
+        <v>0.4527148682990713</v>
       </c>
       <c r="D59">
         <v>264.6216216216216</v>
@@ -2529,7 +2529,7 @@
         <v>1000</v>
       </c>
       <c r="F59">
-        <v>0.06975641858994187</v>
+        <v>0.06895545440624853</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>32.88973317886956</v>
+        <v>32.34936494919539</v>
       </c>
       <c r="C60">
-        <v>0.7778662860263712</v>
+        <v>0.7847182435005258</v>
       </c>
       <c r="D60">
         <v>698.0405405405405</v>
@@ -2566,7 +2566,7 @@
         <v>1000</v>
       </c>
       <c r="F60">
-        <v>0.04711722495859738</v>
+        <v>0.04634310340219647</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>13.90146337527132</v>
+        <v>14.02843521899512</v>
       </c>
       <c r="C61">
-        <v>0.449735340798539</v>
+        <v>0.4412181182810603</v>
       </c>
       <c r="D61">
         <v>161.3108108108108</v>
@@ -2603,7 +2603,7 @@
         <v>1000</v>
       </c>
       <c r="F61">
-        <v>0.08617812597554474</v>
+        <v>0.08696525142042716</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>33.51890011331118</v>
+        <v>33.24250211409304</v>
       </c>
       <c r="C62">
-        <v>0.8410596234557454</v>
+        <v>0.8455644233357791</v>
       </c>
       <c r="D62">
         <v>1211.402777777778</v>
@@ -2640,7 +2640,7 @@
         <v>2000</v>
       </c>
       <c r="F62">
-        <v>0.02766949253228471</v>
+        <v>0.02744132894847226</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>33.50199169180883</v>
+        <v>34.26608048985912</v>
       </c>
       <c r="C63">
-        <v>0.662335207751074</v>
+        <v>0.6497920406505006</v>
       </c>
       <c r="D63">
         <v>644.4583333333334</v>
@@ -2677,7 +2677,7 @@
         <v>2000</v>
       </c>
       <c r="F63">
-        <v>0.05198472881640989</v>
+        <v>0.05317035829550778</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>27.65852664393966</v>
+        <v>28.46569740651707</v>
       </c>
       <c r="C64">
-        <v>0.6116667237643234</v>
+        <v>0.5912857340766019</v>
       </c>
       <c r="D64">
         <v>629.8243243243244</v>
@@ -2714,7 +2714,7 @@
         <v>2000</v>
       </c>
       <c r="F64">
-        <v>0.04391466886200644</v>
+        <v>0.04519624966383297</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>16.08159128053839</v>
+        <v>16.82289152103777</v>
       </c>
       <c r="C65">
-        <v>0.5046887680833628</v>
+        <v>0.4675361997779036</v>
       </c>
       <c r="D65">
         <v>176.1081081081081</v>
@@ -2751,7 +2751,7 @@
         <v>2000</v>
       </c>
       <c r="F65">
-        <v>0.09131658646100685</v>
+        <v>0.09552593405131948</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>29.39793459030772</v>
+        <v>30.30396259050714</v>
       </c>
       <c r="C66">
-        <v>0.3457394819684239</v>
+        <v>0.3207088175145437</v>
       </c>
       <c r="D66">
         <v>560.4324324324324</v>
@@ -2788,7 +2788,7 @@
         <v>2000</v>
       </c>
       <c r="F66">
-        <v>0.0524558053550051</v>
+        <v>0.05407246411307698</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>30.32391772433523</v>
+        <v>30.67403173515297</v>
       </c>
       <c r="C67">
-        <v>0.7498220423276732</v>
+        <v>0.745977831698224</v>
       </c>
       <c r="D67">
         <v>1077.837837837838</v>
@@ -2825,7 +2825,7 @@
         <v>2000</v>
       </c>
       <c r="F67">
-        <v>0.02813402597292887</v>
+        <v>0.02845885592278485</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>28.83137978503152</v>
+        <v>29.00272055304322</v>
       </c>
       <c r="C68">
-        <v>0.8711084526067092</v>
+        <v>0.8692664059369007</v>
       </c>
       <c r="D68">
         <v>1331.351351351351</v>
@@ -2862,7 +2862,7 @@
         <v>2000</v>
       </c>
       <c r="F68">
-        <v>0.02165572578250439</v>
+        <v>0.02178442266468938</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>55.5530221262663</v>
+        <v>57.30858184416392</v>
       </c>
       <c r="C69">
-        <v>0.6267351537248457</v>
+        <v>0.5989136873669778</v>
       </c>
       <c r="D69">
         <v>1606.959459459459</v>
@@ -2899,7 +2899,7 @@
         <v>2000</v>
       </c>
       <c r="F69">
-        <v>0.03457026983428253</v>
+        <v>0.03566274276977783</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>58.00087202169325</v>
+        <v>56.48607022747159</v>
       </c>
       <c r="C70">
-        <v>0.6117892211673363</v>
+        <v>0.6279625032510713</v>
       </c>
       <c r="D70">
         <v>1936.189189189189</v>
@@ -2936,7 +2936,7 @@
         <v>2000</v>
       </c>
       <c r="F70">
-        <v>0.02995620073985748</v>
+        <v>0.02917383825034477</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>70.73782547922769</v>
+        <v>73.38828353806529</v>
       </c>
       <c r="C71">
-        <v>0.8341849042847216</v>
+        <v>0.8214794530287809</v>
       </c>
       <c r="D71">
         <v>1444.905405405405</v>
@@ -2973,7 +2973,7 @@
         <v>2000</v>
       </c>
       <c r="F71">
-        <v>0.0489567173149168</v>
+        <v>0.05079106442782967</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>15.44528810259301</v>
+        <v>15.54743431423089</v>
       </c>
       <c r="C72">
-        <v>0.4639205906693881</v>
+        <v>0.4586758889280891</v>
       </c>
       <c r="D72">
         <v>185.3108108108108</v>
@@ -3010,7 +3010,7 @@
         <v>2000</v>
       </c>
       <c r="F72">
-        <v>0.0833480142632453</v>
+        <v>0.08389922987333813</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>29.06651248098002</v>
+        <v>29.67742727439723</v>
       </c>
       <c r="C73">
-        <v>0.7649319392253149</v>
+        <v>0.7578165654184502</v>
       </c>
       <c r="D73">
         <v>763.9324324324324</v>
@@ -3047,7 +3047,7 @@
         <v>2000</v>
       </c>
       <c r="F73">
-        <v>0.03804853838765495</v>
+        <v>0.03884823580522891</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>16.60462791963297</v>
+        <v>16.95557114760163</v>
       </c>
       <c r="C74">
-        <v>0.763407261574282</v>
+        <v>0.7543175910614675</v>
       </c>
       <c r="D74">
         <v>179.5405405405405</v>
@@ -3084,7 +3084,7 @@
         <v>2000</v>
       </c>
       <c r="F74">
-        <v>0.09248400316519943</v>
+        <v>0.09443867717315374</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>29.41024993226484</v>
+        <v>29.52729716380677</v>
       </c>
       <c r="C75">
-        <v>0.8299361574018339</v>
+        <v>0.8283242644817369</v>
       </c>
       <c r="D75">
         <v>1240.108108108108</v>
@@ -3121,7 +3121,7 @@
         <v>2000</v>
       </c>
       <c r="F75">
-        <v>0.02371587584983435</v>
+        <v>0.02381026054966547</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>33.0949166265965</v>
+        <v>33.44012042779901</v>
       </c>
       <c r="C76">
-        <v>0.8169042233660383</v>
+        <v>0.8124274774535077</v>
       </c>
       <c r="D76">
         <v>1222.675675675676</v>
@@ -3158,7 +3158,7 @@
         <v>2000</v>
       </c>
       <c r="F76">
-        <v>0.02706761677278611</v>
+        <v>0.02734995149823301</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>33.68654860666179</v>
+        <v>34.06364123714877</v>
       </c>
       <c r="C77">
-        <v>0.8098518891989545</v>
+        <v>0.8018733514915142</v>
       </c>
       <c r="D77">
         <v>1347</v>
@@ -3195,7 +3195,7 @@
         <v>2000</v>
       </c>
       <c r="F77">
-        <v>0.02500857357584394</v>
+        <v>0.02528852356135766</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>27.43812366334572</v>
+        <v>28.49179732823116</v>
       </c>
       <c r="C78">
-        <v>0.8526766746142945</v>
+        <v>0.8411033890387655</v>
       </c>
       <c r="D78">
         <v>1091.013513513514</v>
@@ -3232,7 +3232,7 @@
         <v>2000</v>
       </c>
       <c r="F78">
-        <v>0.02514920605793749</v>
+        <v>0.02611498113939563</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>34.33454201344394</v>
+        <v>34.79458542515181</v>
       </c>
       <c r="C79">
-        <v>0.6348696870414564</v>
+        <v>0.6266286393911232</v>
       </c>
       <c r="D79">
         <v>351.1486486486486</v>
@@ -3269,7 +3269,7 @@
         <v>2000</v>
       </c>
       <c r="F79">
-        <v>0.09777779907619211</v>
+        <v>0.09908790923460588</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>29.07968196663659</v>
+        <v>29.44141817649204</v>
       </c>
       <c r="C80">
-        <v>0.6565237920002905</v>
+        <v>0.647723859306977</v>
       </c>
       <c r="D80">
         <v>506.5405405405405</v>
@@ -3306,7 +3306,7 @@
         <v>2000</v>
       </c>
       <c r="F80">
-        <v>0.05740839999816209</v>
+        <v>0.05812253081475859</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>14.10255434082088</v>
+        <v>14.50306795100936</v>
       </c>
       <c r="C81">
-        <v>0.5206518376686023</v>
+        <v>0.4967930602925098</v>
       </c>
       <c r="D81">
         <v>147.2027027027027</v>
@@ -3343,7 +3343,7 @@
         <v>2000</v>
       </c>
       <c r="F81">
-        <v>0.09580363731026759</v>
+        <v>0.09852446785777039</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>29.46718370792117</v>
+        <v>29.83470803181835</v>
       </c>
       <c r="C82">
-        <v>0.8244936761114799</v>
+        <v>0.8197177063353125</v>
       </c>
       <c r="D82">
         <v>1100.662162162162</v>
@@ -3380,7 +3380,7 @@
         <v>2000</v>
       </c>
       <c r="F82">
-        <v>0.02677223286211208</v>
+        <v>0.02710614488028776</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>76.77795015130873</v>
+        <v>77.71277924009659</v>
       </c>
       <c r="C83">
-        <v>0.632011744805139</v>
+        <v>0.6310144359770035</v>
       </c>
       <c r="D83">
         <v>2402.175675675676</v>
@@ -3417,7 +3417,7 @@
         <v>2000</v>
       </c>
       <c r="F83">
-        <v>0.03196183814895756</v>
+        <v>0.03235099748407776</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>56.51043725507086</v>
+        <v>56.7429273753064</v>
       </c>
       <c r="C84">
-        <v>0.8279982434948908</v>
+        <v>0.8259313172772572</v>
       </c>
       <c r="D84">
         <v>1028.351351351351</v>
@@ -3454,7 +3454,7 @@
         <v>2000</v>
       </c>
       <c r="F84">
-        <v>0.05495246073320251</v>
+        <v>0.05517854116760854</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>28.49264900707021</v>
+        <v>29.94126799046387</v>
       </c>
       <c r="C85">
-        <v>0.8550359991655525</v>
+        <v>0.8396730478889839</v>
       </c>
       <c r="D85">
         <v>1186.959459459459</v>
@@ -3491,7 +3491,7 @@
         <v>2000</v>
       </c>
       <c r="F85">
-        <v>0.02400473645498031</v>
+        <v>0.02522518166214296</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>26.69436129067325</v>
+        <v>27.49786729955281</v>
       </c>
       <c r="C86">
-        <v>0.5916794591766583</v>
+        <v>0.573757343611108</v>
       </c>
       <c r="D86">
         <v>450.027027027027</v>
@@ -3528,7 +3528,7 @@
         <v>2000</v>
       </c>
       <c r="F86">
-        <v>0.05931724027114949</v>
+        <v>0.06110270194483538</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>26.3654067826557</v>
+        <v>26.4083995238719</v>
       </c>
       <c r="C87">
-        <v>0.8514885389031173</v>
+        <v>0.8510380648004027</v>
       </c>
       <c r="D87">
         <v>1172.797297297297</v>
@@ -3565,7 +3565,7 @@
         <v>2000</v>
       </c>
       <c r="F87">
-        <v>0.02248078746720732</v>
+        <v>0.02251744575531497</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>10.58028200037903</v>
+        <v>11.06167165544217</v>
       </c>
       <c r="C88">
-        <v>0.53065798981104</v>
+        <v>0.4900264674296426</v>
       </c>
       <c r="D88">
         <v>111.3108108108108</v>
@@ -3602,7 +3602,7 @@
         <v>2000</v>
       </c>
       <c r="F88">
-        <v>0.09505170183659684</v>
+        <v>0.09937643589932263</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>17.97192447200872</v>
+        <v>18.33323627550209</v>
       </c>
       <c r="C89">
-        <v>0.4729889684045651</v>
+        <v>0.4622359743834709</v>
       </c>
       <c r="D89">
         <v>264.6216216216216</v>
@@ -3639,7 +3639,7 @@
         <v>2000</v>
       </c>
       <c r="F89">
-        <v>0.06791555565972041</v>
+        <v>0.06928094599056044</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>32.24348233997185</v>
+        <v>32.45985014187748</v>
       </c>
       <c r="C90">
-        <v>0.7861806886480287</v>
+        <v>0.783761962571346</v>
       </c>
       <c r="D90">
         <v>698.0405405405405</v>
@@ -3676,7 +3676,7 @@
         <v>2000</v>
       </c>
       <c r="F90">
-        <v>0.04619141792968574</v>
+        <v>0.04650138245085536</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>14.3234667093499</v>
+        <v>14.0842944018151</v>
       </c>
       <c r="C91">
-        <v>0.4170134850461387</v>
+        <v>0.4353517499913283</v>
       </c>
       <c r="D91">
         <v>161.3108108108108</v>
@@ -3713,7 +3713,7 @@
         <v>2000</v>
       </c>
       <c r="F91">
-        <v>0.08879421433290549</v>
+        <v>0.08731153436661789</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>25.75401344426399</v>
+        <v>25.38112877730552</v>
       </c>
       <c r="C92">
-        <v>0.9123756582183856</v>
+        <v>0.9171086623134536</v>
       </c>
       <c r="D92">
         <v>1211.402777777778</v>
@@ -3750,7 +3750,7 @@
         <v>5000</v>
       </c>
       <c r="F92">
-        <v>0.02125966187027215</v>
+        <v>0.02095184957712016</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>27.67792602121034</v>
+        <v>26.82706211732242</v>
       </c>
       <c r="C93">
-        <v>0.7671858332887606</v>
+        <v>0.7815408332331053</v>
       </c>
       <c r="D93">
         <v>644.4583333333334</v>
@@ -3787,7 +3787,7 @@
         <v>5000</v>
       </c>
       <c r="F93">
-        <v>0.04294758030057853</v>
+        <v>0.04162730269708011</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>22.78551438272692</v>
+        <v>23.06981286498977</v>
       </c>
       <c r="C94">
-        <v>0.7380012962891185</v>
+        <v>0.7321929417205725</v>
       </c>
       <c r="D94">
         <v>629.8243243243244</v>
@@ -3824,7 +3824,7 @@
         <v>5000</v>
       </c>
       <c r="F94">
-        <v>0.03617757127302319</v>
+        <v>0.03662896457633495</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>16.5320544568426</v>
+        <v>15.56610129523647</v>
       </c>
       <c r="C95">
-        <v>0.4751789581770865</v>
+        <v>0.5337144636040847</v>
       </c>
       <c r="D95">
         <v>176.1081081081081</v>
@@ -3861,7 +3861,7 @@
         <v>5000</v>
       </c>
       <c r="F95">
-        <v>0.09387446514781711</v>
+        <v>0.08838946407669576</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>25.17528980106586</v>
+        <v>24.1691562862928</v>
       </c>
       <c r="C96">
-        <v>0.498405003876852</v>
+        <v>0.53546947788334</v>
       </c>
       <c r="D96">
         <v>560.4324324324324</v>
@@ -3898,7 +3898,7 @@
         <v>5000</v>
       </c>
       <c r="F96">
-        <v>0.04492118646988025</v>
+        <v>0.0431259057963365</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>24.84342747163557</v>
+        <v>24.05382532822741</v>
       </c>
       <c r="C97">
-        <v>0.8345515314870872</v>
+        <v>0.845706804743365</v>
       </c>
       <c r="D97">
         <v>1077.837837837838</v>
@@ -3935,7 +3935,7 @@
         <v>5000</v>
       </c>
       <c r="F97">
-        <v>0.02304931836636199</v>
+        <v>0.02231673864454399</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>21.95353437023492</v>
+        <v>21.77301617765947</v>
       </c>
       <c r="C98">
-        <v>0.9273172353702031</v>
+        <v>0.9279777341316652</v>
       </c>
       <c r="D98">
         <v>1331.351351351351</v>
@@ -3972,7 +3972,7 @@
         <v>5000</v>
       </c>
       <c r="F98">
-        <v>0.01648966243805708</v>
+        <v>0.01635407224062933</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>48.84761292625613</v>
+        <v>49.19371900572445</v>
       </c>
       <c r="C99">
-        <v>0.7087187153974551</v>
+        <v>0.7045862883539166</v>
       </c>
       <c r="D99">
         <v>1606.959459459459</v>
@@ -4009,7 +4009,7 @@
         <v>5000</v>
       </c>
       <c r="F99">
-        <v>0.03039753905346637</v>
+        <v>0.03061291852519539</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>50.00924924257121</v>
+        <v>51.22082278377652</v>
       </c>
       <c r="C100">
-        <v>0.7065623018056368</v>
+        <v>0.6918037358828278</v>
       </c>
       <c r="D100">
         <v>1936.189189189189</v>
@@ -4046,7 +4046,7 @@
         <v>5000</v>
       </c>
       <c r="F100">
-        <v>0.02582869975816433</v>
+        <v>0.02645445138820658</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>57.59716922024127</v>
+        <v>58.00738301058543</v>
       </c>
       <c r="C101">
-        <v>0.8915820846322248</v>
+        <v>0.89030737845518</v>
       </c>
       <c r="D101">
         <v>1444.905405405405</v>
@@ -4083,7 +4083,7 @@
         <v>5000</v>
       </c>
       <c r="F101">
-        <v>0.03986224219576568</v>
+        <v>0.04014614575707118</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>15.74823502043987</v>
+        <v>14.91950714981806</v>
       </c>
       <c r="C102">
-        <v>0.4329004182543308</v>
+        <v>0.4891970935412844</v>
       </c>
       <c r="D102">
         <v>185.3108108108108</v>
@@ -4120,7 +4120,7 @@
         <v>5000</v>
       </c>
       <c r="F102">
-        <v>0.08498281860370092</v>
+        <v>0.08051072187606918</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>25.29328948171862</v>
+        <v>24.84729552882285</v>
       </c>
       <c r="C103">
-        <v>0.8188929571406021</v>
+        <v>0.8284669419858016</v>
       </c>
       <c r="D103">
         <v>763.9324324324324</v>
@@ -4157,7 +4157,7 @@
         <v>5000</v>
       </c>
       <c r="F103">
-        <v>0.03310932800847637</v>
+        <v>0.03252551465802641</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>16.77310620512997</v>
+        <v>15.3974416765634</v>
       </c>
       <c r="C104">
-        <v>0.7590218669723914</v>
+        <v>0.7940153898764142</v>
       </c>
       <c r="D104">
         <v>179.5405405405405</v>
@@ -4194,7 +4194,7 @@
         <v>5000</v>
       </c>
       <c r="F104">
-        <v>0.09342238891913426</v>
+        <v>0.08576025019311244</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>23.10197167893673</v>
+        <v>22.43148052849354</v>
       </c>
       <c r="C105">
-        <v>0.8977512467047134</v>
+        <v>0.9080254344252875</v>
       </c>
       <c r="D105">
         <v>1240.108108108108</v>
@@ -4231,7 +4231,7 @@
         <v>5000</v>
       </c>
       <c r="F105">
-        <v>0.01862899817192614</v>
+        <v>0.01808832664009809</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>25.84758867864158</v>
+        <v>24.99154378916261</v>
       </c>
       <c r="C106">
-        <v>0.891155505342156</v>
+        <v>0.8994279943252369</v>
       </c>
       <c r="D106">
         <v>1222.675675675676</v>
@@ -4268,7 +4268,7 @@
         <v>5000</v>
       </c>
       <c r="F106">
-        <v>0.02114018393664181</v>
+        <v>0.02044004332984851</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>25.71132993689973</v>
+        <v>25.40471675294659</v>
       </c>
       <c r="C107">
-        <v>0.894532460714905</v>
+        <v>0.8947232283249679</v>
       </c>
       <c r="D107">
         <v>1347</v>
@@ -4305,7 +4305,7 @@
         <v>5000</v>
       </c>
       <c r="F107">
-        <v>0.01908784702071249</v>
+        <v>0.01886022030656762</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>22.81412543184859</v>
+        <v>22.85273066468933</v>
       </c>
       <c r="C108">
-        <v>0.8986871673337368</v>
+        <v>0.8997155361322515</v>
       </c>
       <c r="D108">
         <v>1091.013513513514</v>
@@ -4342,7 +4342,7 @@
         <v>5000</v>
       </c>
       <c r="F108">
-        <v>0.02091094670163865</v>
+        <v>0.02094633144468954</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>31.36854057728255</v>
+        <v>31.19773899287437</v>
       </c>
       <c r="C109">
-        <v>0.6889704479600142</v>
+        <v>0.6914194923931566</v>
       </c>
       <c r="D109">
         <v>351.1486486486486</v>
@@ -4379,7 +4379,7 @@
         <v>5000</v>
       </c>
       <c r="F109">
-        <v>0.08933122966014657</v>
+        <v>0.08884482145363491</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>26.62165552115683</v>
+        <v>26.31822657462407</v>
       </c>
       <c r="C110">
-        <v>0.7080481194344417</v>
+        <v>0.7142496820383331</v>
       </c>
       <c r="D110">
         <v>506.5405405405405</v>
@@ -4416,7 +4416,7 @@
         <v>5000</v>
       </c>
       <c r="F110">
-        <v>0.05255582404667607</v>
+        <v>0.05195680200944887</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>13.4150516662477</v>
+        <v>13.42323250646425</v>
       </c>
       <c r="C111">
-        <v>0.5546104060118913</v>
+        <v>0.5508208548674104</v>
       </c>
       <c r="D111">
         <v>147.2027027027027</v>
@@ -4453,7 +4453,7 @@
         <v>5000</v>
       </c>
       <c r="F111">
-        <v>0.09113318858921599</v>
+        <v>0.09118876392897772</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>23.54040862498173</v>
+        <v>22.48687835144256</v>
       </c>
       <c r="C112">
-        <v>0.8889645058644016</v>
+        <v>0.8987944543043492</v>
       </c>
       <c r="D112">
         <v>1100.662162162162</v>
@@ -4490,7 +4490,7 @@
         <v>5000</v>
       </c>
       <c r="F112">
-        <v>0.02138749693978622</v>
+        <v>0.02043031833425518</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>78.88794582583702</v>
+        <v>79.99369768478725</v>
       </c>
       <c r="C113">
-        <v>0.6214342075801175</v>
+        <v>0.6053080350848383</v>
       </c>
       <c r="D113">
         <v>2402.175675675676</v>
@@ -4527,7 +4527,7 @@
         <v>5000</v>
       </c>
       <c r="F113">
-        <v>0.03284020674451617</v>
+        <v>0.03330051939781086</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>42.04274258243325</v>
+        <v>41.0832703632281</v>
       </c>
       <c r="C114">
-        <v>0.9063847760961895</v>
+        <v>0.9101024750974381</v>
       </c>
       <c r="D114">
         <v>1028.351351351351</v>
@@ -4564,7 +4564,7 @@
         <v>5000</v>
       </c>
       <c r="F114">
-        <v>0.04088363624668271</v>
+        <v>0.03995061640094194</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>21.99373663452466</v>
+        <v>22.24712317135883</v>
       </c>
       <c r="C115">
-        <v>0.9177559820778805</v>
+        <v>0.9166482015624681</v>
       </c>
       <c r="D115">
         <v>1186.959459459459</v>
@@ -4601,7 +4601,7 @@
         <v>5000</v>
       </c>
       <c r="F115">
-        <v>0.01852947584624381</v>
+        <v>0.01874295115478515</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>25.68789323741376</v>
+        <v>24.20769531985455</v>
       </c>
       <c r="C116">
-        <v>0.6159736154311058</v>
+        <v>0.6508491886730021</v>
       </c>
       <c r="D116">
         <v>450.027027027027</v>
@@ -4638,7 +4638,7 @@
         <v>5000</v>
       </c>
       <c r="F116">
-        <v>0.05708077891924264</v>
+        <v>0.05379164775897054</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>18.95163617937255</v>
+        <v>19.33074089791536</v>
       </c>
       <c r="C117">
-        <v>0.9248169559062966</v>
+        <v>0.9211798515929954</v>
       </c>
       <c r="D117">
         <v>1172.797297297297</v>
@@ -4675,7 +4675,7 @@
         <v>5000</v>
       </c>
       <c r="F117">
-        <v>0.0161593450317855</v>
+        <v>0.01648259331980293</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>10.18918648610422</v>
+        <v>9.79567011286094</v>
       </c>
       <c r="C118">
-        <v>0.5422992692123314</v>
+        <v>0.5658034714199282</v>
       </c>
       <c r="D118">
         <v>111.3108108108108</v>
@@ -4712,7 +4712,7 @@
         <v>5000</v>
       </c>
       <c r="F118">
-        <v>0.09153815709259588</v>
+        <v>0.08800286370665407</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>17.93030516416779</v>
+        <v>17.70237559531322</v>
       </c>
       <c r="C119">
-        <v>0.4596274145638097</v>
+        <v>0.4770302404298991</v>
       </c>
       <c r="D119">
         <v>264.6216216216216</v>
@@ -4749,7 +4749,7 @@
         <v>5000</v>
       </c>
       <c r="F119">
-        <v>0.06775827709878546</v>
+        <v>0.06689693565790922</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>27.0050425308042</v>
+        <v>26.27007631103873</v>
       </c>
       <c r="C120">
-        <v>0.8506280127237679</v>
+        <v>0.8586865264178797</v>
       </c>
       <c r="D120">
         <v>698.0405405405405</v>
@@ -4786,7 +4786,7 @@
         <v>5000</v>
       </c>
       <c r="F120">
-        <v>0.03868692570476258</v>
+        <v>0.03763402665795888</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>13.65446462244667</v>
+        <v>13.2607277343684</v>
       </c>
       <c r="C121">
-        <v>0.445393266666151</v>
+        <v>0.475244970831814</v>
       </c>
       <c r="D121">
         <v>161.3108108108108</v>
@@ -4823,7 +4823,7 @@
         <v>5000</v>
       </c>
       <c r="F121">
-        <v>0.08464692821153171</v>
+        <v>0.08220606956046426</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>20.4136519270187</v>
+        <v>22.44866795437864</v>
       </c>
       <c r="C122">
-        <v>0.9467969130528651</v>
+        <v>0.9353987143268009</v>
       </c>
       <c r="D122">
         <v>1211.402777777778</v>
@@ -4860,7 +4860,7 @@
         <v>10000</v>
       </c>
       <c r="F122">
-        <v>0.01685125071651719</v>
+        <v>0.01853113462027794</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>21.01956667203738</v>
+        <v>23.74570013505444</v>
       </c>
       <c r="C123">
-        <v>0.8699636929517772</v>
+        <v>0.8304999575066855</v>
       </c>
       <c r="D123">
         <v>644.4583333333334</v>
@@ -4897,7 +4897,7 @@
         <v>10000</v>
       </c>
       <c r="F123">
-        <v>0.03261586604570357</v>
+        <v>0.03684598197719704</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>18.32362028336525</v>
+        <v>19.93415095606923</v>
       </c>
       <c r="C124">
-        <v>0.8324788105569062</v>
+        <v>0.80192614234466</v>
       </c>
       <c r="D124">
         <v>629.8243243243244</v>
@@ -4934,7 +4934,7 @@
         <v>10000</v>
       </c>
       <c r="F124">
-        <v>0.02909322421458211</v>
+        <v>0.0316503351588629</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>13.52353747487447</v>
+        <v>14.46887846571639</v>
       </c>
       <c r="C125">
-        <v>0.6468156778907129</v>
+        <v>0.5969636278529554</v>
       </c>
       <c r="D125">
         <v>176.1081081081081</v>
@@ -4971,7 +4971,7 @@
         <v>10000</v>
       </c>
       <c r="F125">
-        <v>0.07679111211945293</v>
+        <v>0.08215907047751787</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>19.32049254786409</v>
+        <v>22.71366675475226</v>
       </c>
       <c r="C126">
-        <v>0.7049723161977741</v>
+        <v>0.5903278678614082</v>
       </c>
       <c r="D126">
         <v>560.4324324324324</v>
@@ -5008,7 +5008,7 @@
         <v>10000</v>
       </c>
       <c r="F126">
-        <v>0.034474258500722</v>
+        <v>0.04052882281663935</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>20.69522378026065</v>
+        <v>23.52801242394817</v>
       </c>
       <c r="C127">
-        <v>0.8913944073607719</v>
+        <v>0.8539200349788664</v>
       </c>
       <c r="D127">
         <v>1077.837837837838</v>
@@ -5045,7 +5045,7 @@
         <v>10000</v>
       </c>
       <c r="F127">
-        <v>0.01920068404888776</v>
+        <v>0.02182889818671219</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>17.46865040646701</v>
+        <v>19.5797066404405</v>
       </c>
       <c r="C128">
-        <v>0.9557194825977411</v>
+        <v>0.9433125093436622</v>
       </c>
       <c r="D128">
         <v>1331.351351351351</v>
@@ -5082,7 +5082,7 @@
         <v>10000</v>
       </c>
       <c r="F128">
-        <v>0.01312099198212098</v>
+        <v>0.01470664120374134</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>46.06881984734306</v>
+        <v>46.63567761250972</v>
       </c>
       <c r="C129">
-        <v>0.7444130984679844</v>
+        <v>0.7399171683436319</v>
       </c>
       <c r="D129">
         <v>1606.959459459459</v>
@@ -5119,7 +5119,7 @@
         <v>10000</v>
       </c>
       <c r="F129">
-        <v>0.02866831491992925</v>
+        <v>0.02902106667220889</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -5144,10 +5144,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>51.74152328946166</v>
+        <v>49.67317272656491</v>
       </c>
       <c r="C130">
-        <v>0.6887157370694614</v>
+        <v>0.7090568402200689</v>
       </c>
       <c r="D130">
         <v>1936.189189189189</v>
@@ -5156,7 +5156,7 @@
         <v>10000</v>
       </c>
       <c r="F130">
-        <v>0.02672338198062622</v>
+        <v>0.02565512347859269</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>50.43626127726026</v>
+        <v>54.03059071803303</v>
       </c>
       <c r="C131">
-        <v>0.9187215693743753</v>
+        <v>0.9074046073819674</v>
       </c>
       <c r="D131">
         <v>1444.905405405405</v>
@@ -5193,7 +5193,7 @@
         <v>10000</v>
       </c>
       <c r="F131">
-        <v>0.03490627212589676</v>
+        <v>0.03739386019036544</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>13.38484730679732</v>
+        <v>14.54690509495489</v>
       </c>
       <c r="C132">
-        <v>0.5790023504102924</v>
+        <v>0.5084888055826283</v>
       </c>
       <c r="D132">
         <v>185.3108108108108</v>
@@ -5230,7 +5230,7 @@
         <v>10000</v>
       </c>
       <c r="F132">
-        <v>0.07222917674491368</v>
+        <v>0.07850003478645536</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>21.45064028268078</v>
+        <v>22.70661541539257</v>
       </c>
       <c r="C133">
-        <v>0.8742991936874412</v>
+        <v>0.8551935082335103</v>
       </c>
       <c r="D133">
         <v>763.9324324324324</v>
@@ -5267,7 +5267,7 @@
         <v>10000</v>
       </c>
       <c r="F133">
-        <v>0.02807923760270255</v>
+        <v>0.02972332951370134</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>12.77631448556592</v>
+        <v>13.9282396485226</v>
       </c>
       <c r="C134">
-        <v>0.8587771388707912</v>
+        <v>0.832306100170813</v>
       </c>
       <c r="D134">
         <v>179.5405405405405</v>
@@ -5304,7 +5304,7 @@
         <v>10000</v>
       </c>
       <c r="F134">
-        <v>0.07116116753965662</v>
+        <v>0.07757712885674184</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>18.98064321025589</v>
+        <v>21.04081838393516</v>
       </c>
       <c r="C135">
-        <v>0.9360504434963712</v>
+        <v>0.9222351926634125</v>
       </c>
       <c r="D135">
         <v>1240.108108108108</v>
@@ -5341,7 +5341,7 @@
         <v>10000</v>
       </c>
       <c r="F135">
-        <v>0.01530563592492956</v>
+        <v>0.01696692267905154</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>21.54310653531042</v>
+        <v>22.77191943398406</v>
       </c>
       <c r="C136">
-        <v>0.9291646649505633</v>
+        <v>0.9185963410254931</v>
       </c>
       <c r="D136">
         <v>1222.675675675676</v>
@@ -5378,7 +5378,7 @@
         <v>10000</v>
       </c>
       <c r="F136">
-        <v>0.017619641057638</v>
+        <v>0.01862466055963682</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>21.19893969536149</v>
+        <v>23.54576754805771</v>
       </c>
       <c r="C137">
-        <v>0.9337878896114186</v>
+        <v>0.9167783115075535</v>
       </c>
       <c r="D137">
         <v>1347</v>
@@ -5415,7 +5415,7 @@
         <v>10000</v>
       </c>
       <c r="F137">
-        <v>0.01573789138482664</v>
+        <v>0.0174801540817058</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>19.32974787502335</v>
+        <v>20.93522186395379</v>
       </c>
       <c r="C138">
-        <v>0.9276439591248598</v>
+        <v>0.9147693003790219</v>
       </c>
       <c r="D138">
         <v>1091.013513513514</v>
@@ -5452,7 +5452,7 @@
         <v>10000</v>
       </c>
       <c r="F138">
-        <v>0.01771723964515673</v>
+        <v>0.01918878327779254</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>26.64172404298332</v>
+        <v>29.11844540411814</v>
       </c>
       <c r="C139">
-        <v>0.7736919437611401</v>
+        <v>0.7285081259112198</v>
       </c>
       <c r="D139">
         <v>351.1486486486486</v>
@@ -5489,7 +5489,7 @@
         <v>10000</v>
       </c>
       <c r="F139">
-        <v>0.07587021663193248</v>
+        <v>0.08292341581315153</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>21.51120891967897</v>
+        <v>23.46022863402686</v>
       </c>
       <c r="C140">
-        <v>0.8113727239222229</v>
+        <v>0.7735376365840383</v>
       </c>
       <c r="D140">
         <v>506.5405405405405</v>
@@ -5526,7 +5526,7 @@
         <v>10000</v>
       </c>
       <c r="F140">
-        <v>0.04246690481422057</v>
+        <v>0.04631461207229718</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>11.09007014115413</v>
+        <v>12.26022820002804</v>
       </c>
       <c r="C141">
-        <v>0.7028688716554067</v>
+        <v>0.6274552945458542</v>
       </c>
       <c r="D141">
         <v>147.2027027027027</v>
@@ -5563,7 +5563,7 @@
         <v>10000</v>
       </c>
       <c r="F141">
-        <v>0.0753387671390256</v>
+        <v>0.0832880645186886</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>18.82473806594015</v>
+        <v>21.11145817724772</v>
       </c>
       <c r="C142">
-        <v>0.9300841559698404</v>
+        <v>0.9109432862122745</v>
       </c>
       <c r="D142">
         <v>1100.662162162162</v>
@@ -5600,7 +5600,7 @@
         <v>10000</v>
       </c>
       <c r="F142">
-        <v>0.01710310276221403</v>
+        <v>0.01918068859183453</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>83.65580864872894</v>
+        <v>79.64625918839367</v>
       </c>
       <c r="C143">
-        <v>0.5772207387556766</v>
+        <v>0.6037816210636834</v>
       </c>
       <c r="D143">
         <v>2402.175675675676</v>
@@ -5637,7 +5637,7 @@
         <v>10000</v>
       </c>
       <c r="F143">
-        <v>0.03482501696100911</v>
+        <v>0.03315588447376607</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>32.61080500415966</v>
+        <v>35.94787724114801</v>
       </c>
       <c r="C144">
-        <v>0.946235205508055</v>
+        <v>0.9331761321920039</v>
       </c>
       <c r="D144">
         <v>1028.351351351351</v>
@@ -5674,7 +5674,7 @@
         <v>10000</v>
       </c>
       <c r="F144">
-        <v>0.03171173447801276</v>
+        <v>0.03495680459203859</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>19.28576747014717</v>
+        <v>20.03242600343641</v>
       </c>
       <c r="C145">
-        <v>0.9393013070854689</v>
+        <v>0.9339194574985663</v>
       </c>
       <c r="D145">
         <v>1186.959459459459</v>
@@ -5711,7 +5711,7 @@
         <v>10000</v>
       </c>
       <c r="F145">
-        <v>0.01624804227006194</v>
+        <v>0.01687709368992195</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>21.67045953909012</v>
+        <v>23.02236987103595</v>
       </c>
       <c r="C146">
-        <v>0.7164278926769603</v>
+        <v>0.68140152134895</v>
       </c>
       <c r="D146">
         <v>450.027027027027</v>
@@ -5748,7 +5748,7 @@
         <v>10000</v>
       </c>
       <c r="F146">
-        <v>0.04815368464034198</v>
+        <v>0.05115774939813406</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5773,10 +5773,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>15.66678887133349</v>
+        <v>16.7905957477492</v>
       </c>
       <c r="C147">
-        <v>0.9489976135404933</v>
+        <v>0.9423592540941944</v>
       </c>
       <c r="D147">
         <v>1172.797297297297</v>
@@ -5785,7 +5785,7 @@
         <v>10000</v>
       </c>
       <c r="F147">
-        <v>0.01335847968565198</v>
+        <v>0.01431670740241558</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>8.418290387442285</v>
+        <v>9.442434906036231</v>
       </c>
       <c r="C148">
-        <v>0.6885761165045321</v>
+        <v>0.5952175203011146</v>
       </c>
       <c r="D148">
         <v>111.3108108108108</v>
@@ -5822,7 +5822,7 @@
         <v>10000</v>
       </c>
       <c r="F148">
-        <v>0.07562868625357887</v>
+        <v>0.08482945041236872</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>15.42732861420558</v>
+        <v>16.70828811999575</v>
       </c>
       <c r="C149">
-        <v>0.5896755637234109</v>
+        <v>0.5216299552647954</v>
       </c>
       <c r="D149">
         <v>264.6216216216216</v>
@@ -5859,7 +5859,7 @@
         <v>10000</v>
       </c>
       <c r="F149">
-        <v>0.05829957703254075</v>
+        <v>0.06314029827799435</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>21.20063983595224</v>
+        <v>23.55670265061412</v>
       </c>
       <c r="C150">
-        <v>0.9102045175471623</v>
+        <v>0.8876731418282053</v>
       </c>
       <c r="D150">
         <v>698.0405405405405</v>
@@ -5896,7 +5896,7 @@
         <v>10000</v>
       </c>
       <c r="F150">
-        <v>0.03037164549144256</v>
+        <v>0.03374689761195325</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>10.77667967105251</v>
+        <v>12.14164135992036</v>
       </c>
       <c r="C151">
-        <v>0.653064745311002</v>
+        <v>0.5539911779619598</v>
       </c>
       <c r="D151">
         <v>161.3108108108108</v>
@@ -5933,7 +5933,7 @@
         <v>10000</v>
       </c>
       <c r="F151">
-        <v>0.06680692767511819</v>
+        <v>0.07526861528307839</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
